--- a/docs/projetos/capota-bubble/ZG-CAP-02-cotacao.xlsx
+++ b/docs/projetos/capota-bubble/ZG-CAP-02-cotacao.xlsx
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>9.16</v>
+        <v>6.11</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>58</v>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>16.17</v>
+        <v>14.83</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>38</v>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>18.38</v>
+        <v>10.78</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>120</v>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>16.17</v>
+        <v>14.83</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>6</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>16.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>65</v>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>7.4</v>
+        <v>6.87</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>60</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>45° a 120°</t>
+          <t>45° a 89°</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.1</v>
+        <v>90.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12694</v>
+        <v>7447</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51.5</v>
+        <v>48.4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.71</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14971</v>
+        <v>13732</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.4</v>
+        <v>6.87</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
